--- a/assets/results.xlsx
+++ b/assets/results.xlsx
@@ -141,9 +141,6 @@
     <t>формат 2*2 игрока</t>
   </si>
   <si>
-    <t>Мовчан Максим</t>
-  </si>
-  <si>
     <t>Сычёво</t>
   </si>
   <si>
@@ -151,6 +148,10 @@
   </si>
   <si>
     <t>волейбол</t>
+  </si>
+  <si>
+    <t>Мовчан Максим
+Евстафьева Юля</t>
   </si>
 </sst>
 </file>
@@ -186,9 +187,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -492,7 +496,7 @@
         <v>23</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.25">
@@ -500,7 +504,7 @@
         <v>20</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.25">
@@ -529,7 +533,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>6</v>
       </c>
@@ -537,10 +541,10 @@
         <v>2</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="D4" s="1" t="s">
         <v>30</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>33</v>
       </c>
       <c r="F4" s="1" t="s">
         <v>26</v>
